--- a/build/output/observations-summary.xlsx
+++ b/build/output/observations-summary.xlsx
@@ -170,7 +170,7 @@
     <t>CIBMTR Observation Laboratory Results: Priority Variables</t>
   </si>
   <si>
-    <t>https://vsac.nlm.nih.gov/valueset/2.16.840.1.113762.1.4.1295.7/expansion (extensible)</t>
+    <t>http://fhir.nmdp.org/ig/cibmtr-reporting/ValueSet/cibmtr-priority-variables-2022 (extensible)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
